--- a/Андижон_Жонибек ака.xlsx
+++ b/Андижон_Жонибек ака.xlsx
@@ -5,18 +5,18 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shakhrizodaisoeva/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shakhrizodaisoeva/Desktop/Bot data/Prays list/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E59AD11-2666-7748-9637-2B5F47AE0427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D41644-A817-1041-B76F-67075D4C075B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Прайс-лист" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Прайс-лист'!$B$9:$K$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Прайс-лист'!$B$9:$K$29</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
   <si>
     <t>МНН</t>
   </si>
@@ -74,9 +74,6 @@
     <t>с НДС</t>
   </si>
   <si>
-    <t>Ronald Pharmaceutical Pvt. Ltd</t>
-  </si>
-  <si>
     <t>Адинтан р-р. для инф  200 мл №1</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>Зотокам 1,125г пор для инък №1</t>
   </si>
   <si>
-    <t>Исофлокс 500мг блистеры №10</t>
-  </si>
-  <si>
     <t>Рангор р-р для инъек 100 мг 5мл №5</t>
   </si>
   <si>
@@ -147,9 +141,6 @@
   </si>
   <si>
     <t>Ceftriaxone – 1000 mg + tazobactam – 125 mg (Ceftriaxone + tazobactam)</t>
-  </si>
-  <si>
-    <t>Levofloxacin hemihydrate</t>
   </si>
   <si>
     <t>KMA (potassium hydroxide, magnesium oxide, L-aspartic acid)</t>
@@ -201,37 +192,22 @@
     <t>Рогинолит р-р. для инф 100 мл №1</t>
   </si>
   <si>
-    <t>Экситен р-р. для инф 100 мл Nº1</t>
-  </si>
-  <si>
-    <t>Экситен р-р. для инф 200 мл Nº1</t>
-  </si>
-  <si>
     <t>Ангисем р-р. для инф   250 мл №1</t>
   </si>
   <si>
     <t>Бронь</t>
   </si>
   <si>
-    <t>Страна</t>
-  </si>
-  <si>
-    <t>Индия</t>
-  </si>
-  <si>
-    <t>Узбекистан</t>
-  </si>
-  <si>
-    <t>Meglumine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СП ООО "Reka Med Farm" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ООО "Temur Med Farm" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSME Synapse Pharmatech </t>
+    <t>Сухой цена</t>
+  </si>
+  <si>
+    <t>СП ООО "Reka Med Farm" Узбекистан</t>
+  </si>
+  <si>
+    <t>ООО Temur Med Farm Узбекистан</t>
+  </si>
+  <si>
+    <t>MSME Synapse Pharmatech Индия</t>
   </si>
 </sst>
 </file>
@@ -413,7 +389,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,8 +408,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -465,6 +447,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -506,7 +501,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -612,6 +607,24 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="36">
@@ -1048,7 +1061,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A3:M42"/>
+  <dimension ref="A3:M39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
@@ -1103,7 +1116,7 @@
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
       <c r="D7" s="33" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E7" s="33"/>
       <c r="F7" s="33"/>
@@ -1131,7 +1144,7 @@
     </row>
     <row r="9" spans="1:13" ht="83.25" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>4</v>
@@ -1140,28 +1153,28 @@
         <v>3</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="H9" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="I9" s="21" t="s">
         <v>11</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>29</v>
       </c>
       <c r="J9" s="20" t="s">
         <v>2</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="8" customFormat="1" ht="48" customHeight="1">
@@ -1169,33 +1182,33 @@
         <v>1</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="26">
         <v>28</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F10" s="28">
+        <v>47700</v>
+      </c>
+      <c r="G10" s="28">
         <v>95400</v>
       </c>
-      <c r="G10" s="28">
-        <f t="shared" ref="G10:G31" si="0">F10*(1+$G$8%)</f>
-        <v>109709.99999999999</v>
-      </c>
       <c r="H10" s="28">
-        <f>+G10*1.12</f>
-        <v>122875.2</v>
-      </c>
-      <c r="I10" s="29">
+        <f t="shared" ref="H10:H23" si="0">G10*(1+$H$8%)</f>
+        <v>95400</v>
+      </c>
+      <c r="I10" s="28">
+        <f>+H10*1.12</f>
+        <v>106848.00000000001</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10" s="29">
         <v>46388</v>
-      </c>
-      <c r="J10" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="K10" s="29" t="s">
-        <v>60</v>
       </c>
       <c r="M10" s="15"/>
     </row>
@@ -1204,33 +1217,33 @@
         <v>2</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="26">
         <v>28</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F11" s="28">
+        <v>18045.440000000002</v>
+      </c>
+      <c r="G11" s="28">
         <v>37000</v>
       </c>
-      <c r="G11" s="28">
+      <c r="H11" s="28">
         <f t="shared" si="0"/>
-        <v>42550</v>
-      </c>
-      <c r="H11" s="28">
-        <f t="shared" ref="H11:H32" si="1">+G11*1.12</f>
-        <v>47656.000000000007</v>
-      </c>
-      <c r="I11" s="29">
+        <v>37000</v>
+      </c>
+      <c r="I11" s="28">
+        <f t="shared" ref="I11:I29" si="1">+H11*1.12</f>
+        <v>41440.000000000007</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="K11" s="29">
         <v>46296</v>
-      </c>
-      <c r="J11" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="K11" s="29" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="47" customHeight="1">
@@ -1238,33 +1251,33 @@
         <v>3</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D12" s="26">
         <v>40</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F12" s="28">
+        <v>16000</v>
+      </c>
+      <c r="G12" s="28">
         <v>38000</v>
       </c>
-      <c r="G12" s="28">
+      <c r="H12" s="28">
         <f t="shared" si="0"/>
-        <v>43700</v>
-      </c>
-      <c r="H12" s="28">
+        <v>38000</v>
+      </c>
+      <c r="I12" s="28">
         <f t="shared" si="1"/>
-        <v>48944.000000000007</v>
-      </c>
-      <c r="I12" s="29">
-        <v>46357</v>
+        <v>42560.000000000007</v>
       </c>
       <c r="J12" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="29" t="s">
-        <v>60</v>
+      <c r="K12" s="29">
+        <v>46357</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="47" customHeight="1">
@@ -1272,33 +1285,33 @@
         <v>4</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D13" s="26">
         <v>40</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F13" s="28">
+        <v>16800</v>
+      </c>
+      <c r="G13" s="28">
         <v>43000</v>
       </c>
-      <c r="G13" s="28">
+      <c r="H13" s="28">
         <f t="shared" si="0"/>
-        <v>49449.999999999993</v>
-      </c>
-      <c r="H13" s="28">
+        <v>43000</v>
+      </c>
+      <c r="I13" s="28">
         <f t="shared" si="1"/>
-        <v>55384</v>
-      </c>
-      <c r="I13" s="29">
-        <v>46447</v>
+        <v>48160.000000000007</v>
       </c>
       <c r="J13" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="K13" s="29" t="s">
-        <v>60</v>
+      <c r="K13" s="29">
+        <v>46447</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="47" customHeight="1">
@@ -1306,33 +1319,33 @@
         <v>5</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" s="26">
         <v>40</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F14" s="28">
+        <v>25000</v>
+      </c>
+      <c r="G14" s="28">
         <v>55000</v>
       </c>
-      <c r="G14" s="28">
+      <c r="H14" s="28">
         <f t="shared" si="0"/>
-        <v>63249.999999999993</v>
-      </c>
-      <c r="H14" s="28">
+        <v>55000</v>
+      </c>
+      <c r="I14" s="28">
         <f t="shared" si="1"/>
-        <v>70840</v>
-      </c>
-      <c r="I14" s="29">
-        <v>46357</v>
+        <v>61600.000000000007</v>
       </c>
       <c r="J14" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="K14" s="29" t="s">
-        <v>60</v>
+      <c r="K14" s="29">
+        <v>46357</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="47" customHeight="1">
@@ -1340,33 +1353,33 @@
         <v>6</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" s="26">
         <v>240</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F15" s="28">
+        <v>21000</v>
+      </c>
+      <c r="G15" s="28">
         <v>45000</v>
       </c>
-      <c r="G15" s="28">
+      <c r="H15" s="28">
         <f t="shared" si="0"/>
-        <v>51749.999999999993</v>
-      </c>
-      <c r="H15" s="28">
+        <v>45000</v>
+      </c>
+      <c r="I15" s="28">
         <f t="shared" si="1"/>
-        <v>57960</v>
-      </c>
-      <c r="I15" s="29">
-        <v>46296</v>
+        <v>50400.000000000007</v>
       </c>
       <c r="J15" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="K15" s="29" t="s">
-        <v>59</v>
+      <c r="K15" s="29">
+        <v>46296</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="47" customHeight="1">
@@ -1374,33 +1387,33 @@
         <v>7</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D16" s="26">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F16" s="28">
-        <v>41000</v>
+        <v>17024</v>
       </c>
       <c r="G16" s="28">
+        <v>37000</v>
+      </c>
+      <c r="H16" s="28">
         <f t="shared" si="0"/>
-        <v>47149.999999999993</v>
-      </c>
-      <c r="H16" s="28">
+        <v>37000</v>
+      </c>
+      <c r="I16" s="28">
         <f t="shared" si="1"/>
-        <v>52808</v>
-      </c>
-      <c r="I16" s="29">
-        <v>46539</v>
+        <v>41440.000000000007</v>
       </c>
       <c r="J16" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="K16" s="29" t="s">
-        <v>59</v>
+        <v>6</v>
+      </c>
+      <c r="K16" s="29">
+        <v>46327</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="47" customHeight="1">
@@ -1408,33 +1421,33 @@
         <v>8</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D17" s="26">
         <v>40</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F17" s="28">
-        <v>37000</v>
+        <v>31000</v>
       </c>
       <c r="G17" s="28">
+        <v>64700</v>
+      </c>
+      <c r="H17" s="28">
         <f t="shared" si="0"/>
-        <v>42550</v>
-      </c>
-      <c r="H17" s="28">
+        <v>64700</v>
+      </c>
+      <c r="I17" s="28">
         <f t="shared" si="1"/>
-        <v>47656.000000000007</v>
-      </c>
-      <c r="I17" s="29">
-        <v>46327</v>
+        <v>72464</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="K17" s="29" t="s">
-        <v>60</v>
+        <v>55</v>
+      </c>
+      <c r="K17" s="29">
+        <v>46600</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="47" customHeight="1">
@@ -1442,33 +1455,33 @@
         <v>9</v>
       </c>
       <c r="C18" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="26">
         <v>50</v>
       </c>
-      <c r="D18" s="26">
-        <v>40</v>
-      </c>
       <c r="E18" s="27" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F18" s="28">
-        <v>64700</v>
+        <v>40000</v>
       </c>
       <c r="G18" s="28">
+        <v>90000</v>
+      </c>
+      <c r="H18" s="28">
         <f t="shared" si="0"/>
-        <v>74405</v>
-      </c>
-      <c r="H18" s="28">
+        <v>90000</v>
+      </c>
+      <c r="I18" s="28">
         <f t="shared" si="1"/>
-        <v>83333.600000000006</v>
-      </c>
-      <c r="I18" s="29">
+        <v>100800.00000000001</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="K18" s="29">
         <v>46600</v>
-      </c>
-      <c r="J18" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="K18" s="29" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="47" customHeight="1">
@@ -1476,33 +1489,33 @@
         <v>10</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D19" s="26">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F19" s="28">
-        <v>90000</v>
+        <v>19600.000000000004</v>
       </c>
       <c r="G19" s="28">
+        <v>44588</v>
+      </c>
+      <c r="H19" s="28">
         <f t="shared" si="0"/>
-        <v>103499.99999999999</v>
-      </c>
-      <c r="H19" s="28">
+        <v>44588</v>
+      </c>
+      <c r="I19" s="28">
         <f t="shared" si="1"/>
-        <v>115920</v>
-      </c>
-      <c r="I19" s="29">
-        <v>46600</v>
+        <v>49938.560000000005</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="K19" s="29" t="s">
-        <v>60</v>
+        <v>6</v>
+      </c>
+      <c r="K19" s="29">
+        <v>46296</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="47" customHeight="1">
@@ -1510,33 +1523,33 @@
         <v>11</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D20" s="26">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F20" s="28">
-        <v>44588</v>
+        <v>18995.2</v>
       </c>
       <c r="G20" s="28">
+        <v>40700</v>
+      </c>
+      <c r="H20" s="28">
         <f t="shared" si="0"/>
-        <v>51276.2</v>
-      </c>
-      <c r="H20" s="28">
+        <v>40700</v>
+      </c>
+      <c r="I20" s="28">
         <f t="shared" si="1"/>
-        <v>57429.344000000005</v>
-      </c>
-      <c r="I20" s="29">
+        <v>45584.000000000007</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="29">
         <v>46296</v>
-      </c>
-      <c r="J20" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="K20" s="29" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="21" spans="2:11" ht="47" customHeight="1">
@@ -1544,33 +1557,33 @@
         <v>12</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="D21" s="26">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F21" s="28">
-        <v>40700</v>
+        <v>13776.000000000002</v>
       </c>
       <c r="G21" s="28">
+        <v>33500</v>
+      </c>
+      <c r="H21" s="28">
         <f t="shared" si="0"/>
-        <v>46805</v>
-      </c>
-      <c r="H21" s="28">
+        <v>33500</v>
+      </c>
+      <c r="I21" s="28">
         <f t="shared" si="1"/>
-        <v>52421.600000000006</v>
-      </c>
-      <c r="I21" s="29">
+        <v>37520</v>
+      </c>
+      <c r="J21" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" s="29">
         <v>46296</v>
-      </c>
-      <c r="J21" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="29" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="47" customHeight="1">
@@ -1578,33 +1591,33 @@
         <v>13</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="D22" s="26">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F22" s="28">
-        <v>33500</v>
+        <v>18480</v>
       </c>
       <c r="G22" s="28">
+        <v>40000</v>
+      </c>
+      <c r="H22" s="28">
         <f t="shared" si="0"/>
-        <v>38525</v>
-      </c>
-      <c r="H22" s="28">
+        <v>40000</v>
+      </c>
+      <c r="I22" s="28">
         <f t="shared" si="1"/>
-        <v>43148.000000000007</v>
-      </c>
-      <c r="I22" s="29">
-        <v>46296</v>
+        <v>44800.000000000007</v>
       </c>
       <c r="J22" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="K22" s="29" t="s">
-        <v>60</v>
+      <c r="K22" s="29">
+        <v>46296</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="47" customHeight="1">
@@ -1612,101 +1625,101 @@
         <v>14</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D23" s="26">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F23" s="28">
+        <v>18480</v>
+      </c>
+      <c r="G23" s="28">
         <v>40000</v>
       </c>
-      <c r="G23" s="28">
+      <c r="H23" s="28">
         <f t="shared" si="0"/>
-        <v>46000</v>
-      </c>
-      <c r="H23" s="28">
+        <v>40000</v>
+      </c>
+      <c r="I23" s="28">
         <f t="shared" si="1"/>
-        <v>51520.000000000007</v>
-      </c>
-      <c r="I23" s="29">
-        <v>46296</v>
+        <v>44800.000000000007</v>
       </c>
       <c r="J23" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="K23" s="29" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="K23" s="29">
+        <v>46661</v>
       </c>
     </row>
     <row r="24" spans="2:11" ht="47" customHeight="1">
       <c r="B24" s="24">
         <v>15</v>
       </c>
-      <c r="C24" s="25" t="s">
-        <v>27</v>
+      <c r="C24" s="30" t="s">
+        <v>29</v>
       </c>
       <c r="D24" s="26">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F24" s="28">
-        <v>40000</v>
+        <v>23800</v>
       </c>
       <c r="G24" s="28">
-        <f t="shared" si="0"/>
-        <v>46000</v>
+        <v>43167.44</v>
       </c>
       <c r="H24" s="28">
-        <f t="shared" si="1"/>
-        <v>51520.000000000007</v>
-      </c>
-      <c r="I24" s="29">
-        <v>46661</v>
+        <f>G24*1.15</f>
+        <v>49642.555999999997</v>
+      </c>
+      <c r="I24" s="28">
+        <f>H24*1.12</f>
+        <v>55599.66272</v>
       </c>
       <c r="J24" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="K24" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="K24" s="29">
+        <v>46447</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="47" customHeight="1">
+      <c r="B25" s="36">
+        <v>16</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="38">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="2:11" ht="47" customHeight="1">
-      <c r="B25" s="24">
-        <v>16</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="26">
-        <v>200</v>
-      </c>
-      <c r="E25" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="28">
-        <v>44523.3</v>
-      </c>
-      <c r="G25" s="28">
-        <f t="shared" si="0"/>
-        <v>51201.794999999998</v>
-      </c>
-      <c r="H25" s="28">
-        <f t="shared" si="1"/>
-        <v>57346.010400000006</v>
-      </c>
-      <c r="I25" s="29">
-        <v>46447</v>
-      </c>
-      <c r="J25" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="K25" s="29" t="s">
-        <v>59</v>
+      <c r="E25" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="40">
+        <v>72000</v>
+      </c>
+      <c r="G25" s="40">
+        <v>145000</v>
+      </c>
+      <c r="H25" s="40">
+        <f>G25*1.03</f>
+        <v>149350</v>
+      </c>
+      <c r="I25" s="40">
+        <f>H25*1.12</f>
+        <v>167272.00000000003</v>
+      </c>
+      <c r="J25" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="41">
+        <v>46419</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="47" customHeight="1">
@@ -1714,33 +1727,33 @@
         <v>17</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D26" s="26">
         <v>40</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F26" s="28">
+        <v>50000</v>
+      </c>
+      <c r="G26" s="28">
         <v>120000</v>
       </c>
-      <c r="G26" s="28">
-        <f t="shared" si="0"/>
-        <v>138000</v>
-      </c>
       <c r="H26" s="28">
+        <f>G26*(1+$H$8%)</f>
+        <v>120000</v>
+      </c>
+      <c r="I26" s="28">
         <f t="shared" si="1"/>
-        <v>154560.00000000003</v>
-      </c>
-      <c r="I26" s="29">
+        <v>134400</v>
+      </c>
+      <c r="J26" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="K26" s="29">
         <v>46600</v>
-      </c>
-      <c r="J26" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="K26" s="29" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="47" customHeight="1">
@@ -1748,65 +1761,67 @@
         <v>18</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D27" s="26">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F27" s="28">
-        <v>145000</v>
+        <v>20500</v>
       </c>
       <c r="G27" s="28">
-        <f>F27*(1.03)</f>
-        <v>149350</v>
+        <v>41800</v>
       </c>
       <c r="H27" s="28">
+        <f>G27*(1+$H$8%)</f>
+        <v>41800</v>
+      </c>
+      <c r="I27" s="28">
         <f t="shared" si="1"/>
-        <v>167272.00000000003</v>
-      </c>
-      <c r="I27" s="29">
-        <v>46419</v>
+        <v>46816.000000000007</v>
       </c>
       <c r="J27" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="K27" s="29"/>
+        <v>6</v>
+      </c>
+      <c r="K27" s="29">
+        <v>46296</v>
+      </c>
     </row>
     <row r="28" spans="2:11" ht="47" customHeight="1">
       <c r="B28" s="24">
         <v>19</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D28" s="26">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F28" s="28">
-        <v>41800</v>
+        <v>18000</v>
       </c>
       <c r="G28" s="28">
-        <f t="shared" si="0"/>
-        <v>48069.999999999993</v>
+        <v>44588</v>
       </c>
       <c r="H28" s="28">
+        <f>G28*(1+$H$8%)</f>
+        <v>44588</v>
+      </c>
+      <c r="I28" s="28">
         <f t="shared" si="1"/>
-        <v>53838.399999999994</v>
-      </c>
-      <c r="I28" s="29">
-        <v>46296</v>
+        <v>49938.560000000005</v>
       </c>
       <c r="J28" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="K28" s="29" t="s">
-        <v>60</v>
+      <c r="K28" s="29">
+        <v>46296</v>
       </c>
     </row>
     <row r="29" spans="2:11" ht="47" customHeight="1">
@@ -1814,139 +1829,62 @@
         <v>20</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D29" s="26">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F29" s="28">
-        <v>44588</v>
+        <v>33000</v>
       </c>
       <c r="G29" s="28">
-        <f t="shared" si="0"/>
-        <v>51276.2</v>
+        <v>65000</v>
       </c>
       <c r="H29" s="28">
+        <f>G29*(1+$H$8%)</f>
+        <v>65000</v>
+      </c>
+      <c r="I29" s="28">
         <f t="shared" si="1"/>
-        <v>57429.344000000005</v>
-      </c>
-      <c r="I29" s="29">
-        <v>46296</v>
+        <v>72800</v>
       </c>
       <c r="J29" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="K29" s="29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" ht="40">
-      <c r="B30" s="24">
-        <v>21</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="26">
-        <v>50</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="28">
-        <v>65000</v>
-      </c>
-      <c r="G30" s="28">
-        <f t="shared" si="0"/>
-        <v>74750</v>
-      </c>
-      <c r="H30" s="28">
-        <f t="shared" si="1"/>
-        <v>83720.000000000015</v>
-      </c>
-      <c r="I30" s="29">
+        <v>55</v>
+      </c>
+      <c r="K29" s="29">
         <v>46600</v>
       </c>
-      <c r="J30" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="K30" s="29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="24">
-        <v>22</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="26">
-        <v>40</v>
-      </c>
-      <c r="E31" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="28">
-        <v>45000</v>
-      </c>
-      <c r="G31" s="28">
-        <f t="shared" si="0"/>
-        <v>51749.999999999993</v>
-      </c>
-      <c r="H31" s="28">
-        <f t="shared" si="1"/>
-        <v>57960</v>
-      </c>
-      <c r="I31" s="29">
-        <v>46631</v>
-      </c>
-      <c r="J31" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="K31" s="29" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="24">
-        <v>23</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="26">
-        <v>20</v>
-      </c>
-      <c r="E32" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F32" s="28">
-        <v>55000</v>
-      </c>
-      <c r="G32" s="28">
-        <f>F32*(1+$G$8%)</f>
-        <v>63249.999999999993</v>
-      </c>
-      <c r="H32" s="28">
-        <f t="shared" si="1"/>
-        <v>70840</v>
-      </c>
-      <c r="I32" s="29">
-        <v>46539</v>
-      </c>
-      <c r="J32" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="K32" s="29" t="s">
-        <v>60</v>
-      </c>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="32" spans="2:11" ht="130" customHeight="1">
+      <c r="B32" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="34"/>
     </row>
     <row r="33" spans="2:11">
-      <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1957,64 +1895,39 @@
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
     </row>
-    <row r="35" spans="2:11" ht="130" customHeight="1">
-      <c r="B35" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
+    <row r="34" spans="2:11">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="K35" s="17"/>
     </row>
     <row r="36" spans="2:11">
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
+      <c r="K36" s="23"/>
     </row>
     <row r="37" spans="2:11">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+      <c r="K37" s="23"/>
     </row>
     <row r="38" spans="2:11">
       <c r="K38" s="17"/>
     </row>
-    <row r="39" spans="2:11">
-      <c r="K39" s="23"/>
-    </row>
-    <row r="40" spans="2:11">
-      <c r="K40" s="23"/>
-    </row>
-    <row r="41" spans="2:11">
-      <c r="K41" s="17"/>
-    </row>
-    <row r="42" spans="2:11" ht="25" customHeight="1">
-      <c r="K42" s="1"/>
+    <row r="39" spans="2:11" ht="25" customHeight="1">
+      <c r="K39" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="B9:K32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B9:K29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="4">
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="B32:K32"/>
     <mergeCell ref="C6:J6"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
